--- a/SQL/Normalizacion/Normalizacion-ejercicio-2.xlsx
+++ b/SQL/Normalizacion/Normalizacion-ejercicio-2.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MarcoLopez\Downloads\Repos\DUAD\DUAD\SQL\Normalizacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C9FCE68-0517-4C83-8F66-93B7439A243F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C18ED503-CEF8-4D14-871E-91CC35ACD4C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8A39CF86-3CF6-4939-98EE-4D305CF1E3C4}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8A39CF86-3CF6-4939-98EE-4D305CF1E3C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabla_original" sheetId="3" r:id="rId1"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId2"/>
-    <sheet name="Sheet6" sheetId="6" r:id="rId3"/>
-    <sheet name="Sheet7" sheetId="7" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="9" r:id="rId3"/>
+    <sheet name="Sheet6" sheetId="6" r:id="rId4"/>
+    <sheet name="Sheet7" sheetId="7" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="42">
   <si>
     <t>VIN</t>
   </si>
@@ -752,16 +753,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D52D57EC-2F27-46B9-96AD-7A81FD3C4242}">
-  <dimension ref="E10:I13"/>
+  <dimension ref="E10:H13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="10" spans="5:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="5:8" x14ac:dyDescent="0.35">
       <c r="E10" s="1" t="s">
         <v>0</v>
       </c>
@@ -769,63 +769,51 @@
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="5:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="5:8" x14ac:dyDescent="0.35">
       <c r="E11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H11" s="2">
+      <c r="G11" s="2">
         <v>2003</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="5:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="5:8" x14ac:dyDescent="0.35">
       <c r="E12" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" s="2">
+      <c r="G12" s="2">
         <v>2014</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="5:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="5:8" x14ac:dyDescent="0.35">
       <c r="E13" s="2" t="s">
         <v>29</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13" s="2">
+      <c r="G13" s="2">
         <v>2015</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="H13" s="2" t="s">
         <v>32</v>
       </c>
     </row>
@@ -835,6 +823,48 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36C52D1E-AE11-4956-B18C-F753F25DFB41}">
+  <dimension ref="E7:F10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="7" spans="5:6" x14ac:dyDescent="0.35">
+      <c r="E7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="5:6" x14ac:dyDescent="0.35">
+      <c r="E8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="5:6" x14ac:dyDescent="0.35">
+      <c r="E9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="5:6" x14ac:dyDescent="0.35">
+      <c r="E10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F11F540-7C2D-4C47-92B4-37FE4480965E}">
   <dimension ref="E10:G14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -904,88 +934,129 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ABC76E9-6B40-477A-BFE0-78F2EA611807}">
-  <dimension ref="E12:H16"/>
+  <dimension ref="E9:G13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="13.26953125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="12" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E12" s="1" t="s">
+    <row r="9" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E9" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="5:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="2">
+        <v>101</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="2">
+        <v>102</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="2">
+        <v>103</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="5:7" x14ac:dyDescent="0.35">
       <c r="E13" s="2" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F13" s="2">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="2">
-        <v>102</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E15" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" s="2">
-        <v>103</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="2">
-        <v>104</v>
-      </c>
-      <c r="G16" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D79C9B6-CD9A-4EB3-AE96-75D943FAC397}">
+  <dimension ref="F10:G14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="6" max="6" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="10" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>